--- a/Results/Study 2/VGG16/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG16/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="C2">
-        <v>384</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="C3">
-        <v>384</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C3">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/VGG16/Confusion Matrices.xlsx
+++ b/Results/Study 2/VGG16/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="C2">
-        <v>416</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="C3">
-        <v>416</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C3">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
